--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_132_R14.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_132_R14.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>T. JONES</t>
+          <t>D. WASHINGTON</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.1435</v>
+        <v>10.6948</v>
       </c>
       <c r="E2" t="n">
-        <v>8.841900000000001</v>
+        <v>8.869899999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>2.3017</v>
+        <v>1.8249</v>
       </c>
       <c r="G2" t="n">
-        <v>4.0385</v>
+        <v>7.9097</v>
       </c>
       <c r="H2" t="n">
-        <v>4.4533</v>
+        <v>1.2914</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4148</v>
+        <v>6.6182</v>
       </c>
       <c r="J2" t="n">
-        <v>4.782</v>
+        <v>8.366899999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>4.5611</v>
+        <v>1.1665</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2208</v>
+        <v>7.2003</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.7433999999999999</v>
+        <v>-0.4572</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.1078</v>
+        <v>0.1249</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.6356000000000001</v>
+        <v>-0.5821</v>
       </c>
       <c r="P2" t="n">
-        <v>1.8556</v>
+        <v>2.7834</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>3.0154</v>
+        <v>2.7834</v>
       </c>
       <c r="S2" t="n">
-        <v>4.9658</v>
+        <v>1.0429</v>
       </c>
       <c r="T2" t="n">
-        <v>4.4</v>
+        <v>0.472</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5658</v>
+        <v>0.5709</v>
       </c>
       <c r="V2" t="n">
-        <v>0.2836</v>
+        <v>-1.0412</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8197</v>
+        <v>0.031</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.5361</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. WASHINGTON</t>
+          <t>T. JONES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>9.465199999999999</v>
+        <v>8.0768</v>
       </c>
       <c r="E3" t="n">
-        <v>7.8083</v>
+        <v>5.7751</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6569</v>
+        <v>2.3017</v>
       </c>
       <c r="G3" t="n">
-        <v>7.9097</v>
+        <v>4.0385</v>
       </c>
       <c r="H3" t="n">
-        <v>1.2914</v>
+        <v>4.4533</v>
       </c>
       <c r="I3" t="n">
-        <v>6.6182</v>
+        <v>-0.4148</v>
       </c>
       <c r="J3" t="n">
-        <v>8.366899999999999</v>
+        <v>4.782</v>
       </c>
       <c r="K3" t="n">
-        <v>1.1665</v>
+        <v>4.5611</v>
       </c>
       <c r="L3" t="n">
-        <v>7.2003</v>
+        <v>0.2208</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.4572</v>
+        <v>-0.7433999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1249</v>
+        <v>-0.1078</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.5821</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>2.7834</v>
+        <v>1.8556</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R3" t="n">
-        <v>2.7834</v>
+        <v>3.0154</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1867</v>
+        <v>1.8991</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5895</v>
+        <v>1.3333</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4028</v>
+        <v>0.5658</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.0412</v>
+        <v>0.2836</v>
       </c>
       <c r="W3" t="n">
-        <v>0.031</v>
+        <v>0.8197</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0722</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6812</v>
+        <v>2.0858</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1333</v>
+        <v>0.3385</v>
       </c>
       <c r="F4" t="n">
-        <v>1.8145</v>
+        <v>1.7473</v>
       </c>
       <c r="G4" t="n">
         <v>-0.9209000000000001</v>
@@ -766,13 +766,13 @@
         <v>2.7834</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8909</v>
+        <v>1.2955</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1019</v>
+        <v>0.3699</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9928</v>
+        <v>0.9256</v>
       </c>
       <c r="V4" t="n">
         <v>-1.0722</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5643</v>
+        <v>0.362</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.6826</v>
+        <v>-0.9185</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2469</v>
+        <v>1.2805</v>
       </c>
       <c r="G5" t="n">
         <v>-1.5748</v>
@@ -844,13 +844,13 @@
         <v>3.0154</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9071</v>
+        <v>0.7049</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5351</v>
+        <v>0.2992</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3721</v>
+        <v>0.4057</v>
       </c>
       <c r="V5" t="n">
         <v>0.5361</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. POKUSEVSKI</t>
+          <t>J. PARKER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.717</v>
+        <v>-1.7252</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.2888</v>
+        <v>-2.7195</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4282</v>
+        <v>0.9943</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.4627</v>
+        <v>-1.988</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6196</v>
+        <v>-1.6567</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8431</v>
+        <v>-0.3312</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.7661</v>
+        <v>-1.2445</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.7661</v>
+        <v>-1.5489</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.3044</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6966</v>
+        <v>-0.7433999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1465</v>
+        <v>-0.1078</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8431</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.8556</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>3.0154</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2544</v>
+        <v>0.5515</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5228</v>
+        <v>0.0791</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2684</v>
+        <v>0.4725</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.3943</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.7501</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. PARKER</t>
+          <t>A. POKUSEVSKI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.3651</v>
+        <v>-1.7506</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.1914</v>
+        <v>-1.2888</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8263</v>
+        <v>-0.4618</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.988</v>
+        <v>-1.4627</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.6567</v>
+        <v>-0.6196</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3312</v>
+        <v>-0.8431</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.2445</v>
+        <v>-0.7661</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.5489</v>
+        <v>-0.7661</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3044</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7433999999999999</v>
+        <v>-0.6966</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1078</v>
+        <v>0.1465</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6356000000000001</v>
+        <v>-0.8431</v>
       </c>
       <c r="P7" t="n">
-        <v>1.8556</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>3.0154</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0883</v>
+        <v>-0.288</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3927</v>
+        <v>-0.5228</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3044</v>
+        <v>0.2348</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.1444</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.3943</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.7501</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.8285</v>
+        <v>-2.3066</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.1066</v>
+        <v>-0.7527</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.722</v>
+        <v>-1.5539</v>
       </c>
       <c r="G8" t="n">
         <v>-2.2684</v>
@@ -1078,13 +1078,13 @@
         <v>1.1598</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.7199</v>
+        <v>-1.198</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.3364</v>
+        <v>-0.9825</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3835</v>
+        <v>-0.2155</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B. FERNANDO</t>
+          <t>V. MARINKOVIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.8535</v>
+        <v>-2.68</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8194</v>
+        <v>-2.5552</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.0341</v>
+        <v>-0.1249</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.9782</v>
+        <v>-3.7512</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1091</v>
+        <v>-0.3684</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.0873</v>
+        <v>-3.3828</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3831</v>
+        <v>-2.2609</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3095</v>
+        <v>0.222</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0736</v>
+        <v>-2.4829</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.3613</v>
+        <v>-1.4903</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2004</v>
+        <v>-0.5904</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.1609</v>
+        <v>-0.8999</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.232</v>
+        <v>1.8556</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9278</v>
+        <v>1.8556</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3593</v>
+        <v>-0.3901</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1845</v>
+        <v>-0.436</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5439000000000001</v>
+        <v>0.0459</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.0026</v>
+        <v>-0.3943</v>
       </c>
       <c r="W9" t="n">
         <v>0.1418</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.1444</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>V. MARINKOVIC</t>
+          <t>B. FERNANDO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.6065</v>
+        <v>-3.3582</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.3808</v>
+        <v>-1.0553</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2257</v>
+        <v>-2.3029</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.7512</v>
+        <v>-0.9782</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3684</v>
+        <v>0.1091</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.3828</v>
+        <v>-1.0873</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.2609</v>
+        <v>0.3831</v>
       </c>
       <c r="K10" t="n">
-        <v>0.222</v>
+        <v>0.3095</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.4829</v>
+        <v>0.0736</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.4903</v>
+        <v>-1.3613</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5904</v>
+        <v>-0.2004</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8999</v>
+        <v>-1.1609</v>
       </c>
       <c r="P10" t="n">
-        <v>1.8556</v>
+        <v>-0.232</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8556</v>
+        <v>0.9278</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3166</v>
+        <v>-0.1454</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.2617</v>
+        <v>-0.4204</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0549</v>
+        <v>0.275</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3943</v>
+        <v>-2.0026</v>
       </c>
       <c r="W10" t="n">
         <v>0.1418</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5361</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.077</v>
+        <v>-3.992</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.0346</v>
+        <v>-3.6808</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0424</v>
+        <v>-0.3112</v>
       </c>
       <c r="G11" t="n">
         <v>-3.5728</v>
@@ -1312,13 +1312,13 @@
         <v>1.1598</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0403</v>
+        <v>-0.9553</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.4857</v>
+        <v>-1.1319</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4455</v>
+        <v>0.1766</v>
       </c>
       <c r="V11" t="n">
         <v>0.5361</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.406599999999997</v>
+        <v>5.4068</v>
       </c>
       <c r="E12" t="n">
-        <v>2.012700000000002</v>
+        <v>2.012699999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>3.393899999999999</v>
+        <v>3.394</v>
       </c>
       <c r="G12" t="n">
         <v>-4.5688</v>
@@ -1390,10 +1390,10 @@
         <v>19.716</v>
       </c>
       <c r="S12" t="n">
-        <v>2.516899999999999</v>
+        <v>2.5171</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9400999999999995</v>
+        <v>-0.9400999999999998</v>
       </c>
       <c r="U12" t="n">
         <v>3.4573</v>
@@ -1405,13 +1405,13 @@
         <v>3.9566</v>
       </c>
       <c r="X12" t="n">
-        <v>-9.2555</v>
+        <v>-9.255500000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>V. LUCIC</t>
+          <t>S. DINWIDDIE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.2554</v>
+        <v>6.2013</v>
       </c>
       <c r="E13" t="n">
-        <v>4.9619</v>
+        <v>4.9944</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2935</v>
+        <v>1.2069</v>
       </c>
       <c r="G13" t="n">
-        <v>2.9163</v>
+        <v>1.9771</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8117</v>
+        <v>1.5223</v>
       </c>
       <c r="I13" t="n">
-        <v>2.1045</v>
+        <v>0.4548</v>
       </c>
       <c r="J13" t="n">
-        <v>2.9886</v>
+        <v>1.4204</v>
       </c>
       <c r="K13" t="n">
-        <v>1.6672</v>
+        <v>1.9059</v>
       </c>
       <c r="L13" t="n">
-        <v>1.3215</v>
+        <v>-0.4855</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.07240000000000001</v>
+        <v>0.5567</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.8555</v>
+        <v>-0.3837</v>
       </c>
       <c r="O13" t="n">
-        <v>0.7831</v>
+        <v>0.9403</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="Q13" t="n">
         <v>-0.232</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1598</v>
+        <v>1.3917</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5913</v>
+        <v>-0.5465</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4753</v>
+        <v>-0.6247</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.116</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>2.0026</v>
+        <v>3.6109</v>
       </c>
       <c r="W13" t="n">
-        <v>2.6805</v>
+        <v>4.4306</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-0.8197</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S. DINWIDDIE</t>
+          <t>V. LUCIC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.2146</v>
+        <v>5.8388</v>
       </c>
       <c r="E14" t="n">
-        <v>4.9944</v>
+        <v>4.9619</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2203</v>
+        <v>0.8769</v>
       </c>
       <c r="G14" t="n">
-        <v>1.9771</v>
+        <v>2.9163</v>
       </c>
       <c r="H14" t="n">
-        <v>1.5223</v>
+        <v>0.8117</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4548</v>
+        <v>2.1045</v>
       </c>
       <c r="J14" t="n">
-        <v>1.4204</v>
+        <v>2.9886</v>
       </c>
       <c r="K14" t="n">
-        <v>1.9059</v>
+        <v>1.6672</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.4855</v>
+        <v>1.3215</v>
       </c>
       <c r="M14" t="n">
-        <v>0.5567</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.3837</v>
+        <v>-0.8555</v>
       </c>
       <c r="O14" t="n">
-        <v>0.9403</v>
+        <v>0.7831</v>
       </c>
       <c r="P14" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="Q14" t="n">
         <v>-0.232</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3917</v>
+        <v>1.1598</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.5332</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6247</v>
+        <v>-0.4753</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.9085</v>
+        <v>0.4674</v>
       </c>
       <c r="V14" t="n">
-        <v>3.6109</v>
+        <v>2.0026</v>
       </c>
       <c r="W14" t="n">
-        <v>4.4306</v>
+        <v>2.6805</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.8197</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. VOIGTMANN</t>
+          <t>I. MIKE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2124</v>
+        <v>1.0021</v>
       </c>
       <c r="E15" t="n">
-        <v>-3.2006</v>
+        <v>-1.0088</v>
       </c>
       <c r="F15" t="n">
-        <v>4.413</v>
+        <v>2.0109</v>
       </c>
       <c r="G15" t="n">
-        <v>2.6148</v>
+        <v>0.8559</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.6709000000000001</v>
+        <v>-0.1211</v>
       </c>
       <c r="I15" t="n">
-        <v>3.2857</v>
+        <v>0.977</v>
       </c>
       <c r="J15" t="n">
-        <v>2.5191</v>
+        <v>0.4848</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.1408</v>
+        <v>-0.1275</v>
       </c>
       <c r="L15" t="n">
-        <v>2.6599</v>
+        <v>0.6122</v>
       </c>
       <c r="M15" t="n">
-        <v>0.09569999999999999</v>
+        <v>0.3711</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5302</v>
+        <v>0.0063</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6258</v>
+        <v>0.3648</v>
       </c>
       <c r="P15" t="n">
-        <v>-4.639</v>
+        <v>-0.232</v>
       </c>
       <c r="Q15" t="n">
-        <v>-6.0307</v>
+        <v>-1.3917</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3917</v>
+        <v>1.1598</v>
       </c>
       <c r="S15" t="n">
-        <v>3.7727</v>
+        <v>0.5199</v>
       </c>
       <c r="T15" t="n">
-        <v>0.311</v>
+        <v>-0.1019</v>
       </c>
       <c r="U15" t="n">
-        <v>3.4617</v>
+        <v>0.6218</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.5361</v>
+        <v>-0.1418</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5361</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. MIKE</t>
+          <t>X. RATHAN-MAYES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5424</v>
+        <v>0.1894</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.0088</v>
+        <v>2.0947</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5512</v>
+        <v>-1.9053</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8559</v>
+        <v>1.8979</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1211</v>
+        <v>-0.24</v>
       </c>
       <c r="I16" t="n">
-        <v>0.977</v>
+        <v>2.138</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4848</v>
+        <v>3.5099</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.1275</v>
+        <v>0.0035</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6122</v>
+        <v>3.5064</v>
       </c>
       <c r="M16" t="n">
-        <v>0.3711</v>
+        <v>-1.612</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0063</v>
+        <v>-0.2435</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3648</v>
+        <v>-1.3684</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.232</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.3917</v>
+        <v>-1.1598</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1598</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0602</v>
+        <v>-0.407</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1019</v>
+        <v>-0.2555</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1621</v>
+        <v>-0.1516</v>
       </c>
       <c r="V16" t="n">
         <v>-0.1418</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X. RATHAN-MAYES</t>
+          <t>J. HOLLATZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1386</v>
+        <v>-0.7173</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9767</v>
+        <v>1.1101</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.8381</v>
+        <v>-1.8274</v>
       </c>
       <c r="G17" t="n">
-        <v>1.8979</v>
+        <v>-1.6036</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.24</v>
+        <v>-0.1883</v>
       </c>
       <c r="I17" t="n">
-        <v>2.138</v>
+        <v>-1.4153</v>
       </c>
       <c r="J17" t="n">
-        <v>3.5099</v>
+        <v>0.144</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0035</v>
+        <v>0.0336</v>
       </c>
       <c r="L17" t="n">
-        <v>3.5064</v>
+        <v>0.1104</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.612</v>
+        <v>-1.7477</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2435</v>
+        <v>-0.222</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.3684</v>
+        <v>-1.5257</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4577</v>
+        <v>-0.1858</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3734</v>
+        <v>-0.1061</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0843</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1418</v>
+        <v>1.0722</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. HOLLATZ</t>
+          <t>J. VOIGTMANN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0705</v>
+        <v>-1.1021</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9922</v>
+        <v>-3.7904</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.0626</v>
+        <v>2.6883</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.6036</v>
+        <v>2.6148</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1883</v>
+        <v>-0.6709000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.4153</v>
+        <v>3.2857</v>
       </c>
       <c r="J18" t="n">
-        <v>0.144</v>
+        <v>2.5191</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0336</v>
+        <v>-0.1408</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1104</v>
+        <v>2.6599</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.7477</v>
+        <v>0.09569999999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.222</v>
+        <v>-0.5302</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.5257</v>
+        <v>0.6258</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-4.639</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-6.0307</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.3917</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.539</v>
+        <v>1.4583</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.224</v>
+        <v>-0.2787</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.315</v>
+        <v>1.737</v>
       </c>
       <c r="V18" t="n">
-        <v>1.0722</v>
+        <v>-0.5361</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>N. GIFFEY</t>
+          <t>A. OBST</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.1391</v>
+        <v>-1.5325</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.1587</v>
+        <v>-2.7031</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0196</v>
+        <v>1.1706</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.2188</v>
+        <v>0.9413</v>
       </c>
       <c r="H19" t="n">
-        <v>0.143</v>
+        <v>-1.4811</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.3618</v>
+        <v>2.4223</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6254999999999999</v>
+        <v>0.5203</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0504</v>
+        <v>-1.119</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6758999999999999</v>
+        <v>1.6393</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5933</v>
+        <v>0.421</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0926</v>
+        <v>-0.3621</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6859</v>
+        <v>0.7831</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.9278</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1598</v>
+        <v>-2.5515</v>
       </c>
       <c r="R19" t="n">
-        <v>0.232</v>
+        <v>1.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0337</v>
+        <v>-0.2418</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3734</v>
+        <v>-0.6719000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6603</v>
+        <v>0.4301</v>
       </c>
       <c r="V19" t="n">
-        <v>1.0412</v>
+        <v>-1.0722</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.0412</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. OBST</t>
+          <t>N. GIFFEY</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.9073</v>
+        <v>-1.7631</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.2928</v>
+        <v>-2.0407</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3855</v>
+        <v>0.2777</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9413</v>
+        <v>-1.2188</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.4811</v>
+        <v>0.143</v>
       </c>
       <c r="I20" t="n">
-        <v>2.4223</v>
+        <v>-1.3618</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5203</v>
+        <v>-0.6254999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.119</v>
+        <v>0.0504</v>
       </c>
       <c r="L20" t="n">
-        <v>1.6393</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>0.421</v>
+        <v>-0.5933</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3621</v>
+        <v>0.0926</v>
       </c>
       <c r="O20" t="n">
-        <v>0.7831</v>
+        <v>-0.6859</v>
       </c>
       <c r="P20" t="n">
+        <v>-0.9278</v>
+      </c>
+      <c r="Q20" t="n">
         <v>-1.1598</v>
       </c>
-      <c r="Q20" t="n">
-        <v>-2.5515</v>
-      </c>
       <c r="R20" t="n">
-        <v>1.3917</v>
+        <v>0.232</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.6166</v>
+        <v>-0.6576</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.2617</v>
+        <v>-0.2555</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3549</v>
+        <v>-0.4022</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.0722</v>
+        <v>1.0412</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0722</v>
+        <v>1.0412</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.1072</v>
+        <v>-3.0229</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.1587</v>
+        <v>-2.0407</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9486</v>
+        <v>-0.9822</v>
       </c>
       <c r="G21" t="n">
         <v>-1.7441</v>
@@ -2092,13 +2092,13 @@
         <v>0.232</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4353</v>
+        <v>-0.351</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3734</v>
+        <v>-0.2555</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0619</v>
+        <v>-0.0955</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.2396</v>
+        <v>-4.4197</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.8567</v>
+        <v>-3.3285</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.383</v>
+        <v>-1.0913</v>
       </c>
       <c r="G22" t="n">
         <v>-1.0978</v>
@@ -2170,13 +2170,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3374</v>
+        <v>0.1573</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5623</v>
+        <v>0.0905</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2249</v>
+        <v>0.0668</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.3064</v>
+        <v>-4.508</v>
       </c>
       <c r="E23" t="n">
         <v>-1.6429</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.6635</v>
+        <v>-2.8652</v>
       </c>
       <c r="G23" t="n">
         <v>-0.9702</v>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4806</v>
+        <v>-0.6822</v>
       </c>
       <c r="T23" t="n">
         <v>-0.5228</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0422</v>
+        <v>-0.1595</v>
       </c>
       <c r="V23" t="n">
         <v>-0.5361</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.406700000000003</v>
+        <v>-3.834000000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.394000000000002</v>
+        <v>-3.394000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.012700000000001</v>
+        <v>-0.4401000000000002</v>
       </c>
       <c r="G24" t="n">
         <v>4.5688</v>
@@ -2305,7 +2305,7 @@
         <v>1.5409</v>
       </c>
       <c r="L24" t="n">
-        <v>8.982700000000001</v>
+        <v>8.982699999999999</v>
       </c>
       <c r="M24" t="n">
         <v>-5.955</v>
@@ -2326,13 +2326,13 @@
         <v>6.958699999999999</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.5171</v>
+        <v>-0.9442999999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>-3.4573</v>
+        <v>-3.4574</v>
       </c>
       <c r="U24" t="n">
-        <v>0.9402000000000003</v>
+        <v>2.512800000000001</v>
       </c>
       <c r="V24" t="n">
         <v>5.2989</v>
